--- a/nmtcapp/templates/pipeline_sample.xlsx
+++ b/nmtcapp/templates/pipeline_sample.xlsx
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -293,6 +293,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,6 +709,11 @@
           <t>Identity</t>
         </is>
       </c>
+      <c r="J2" s="32" t="inlineStr">
+        <is>
+          <t>Application Request</t>
+        </is>
+      </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Business Strategy</t>
@@ -930,7 +938,7 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>CY2025</t>
+          <t>CY2026</t>
         </is>
       </c>
       <c r="L4" s="10" t="n">
@@ -1011,12 +1019,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="Z2:AB2"/>
     <mergeCell ref="T2:Y2"/>
     <mergeCell ref="L2:S2"/>
     <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="A5:O5"/>
     <mergeCell ref="A1:AD1"/>
   </mergeCells>
@@ -1046,7 +1055,7 @@
       <formula1>"nonprofit,for_profit,government"</formula1>
     </dataValidation>
     <dataValidation sqref="K4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"CY2025,CY2026"</formula1>
+      <formula1>"CY2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2529,7 +2538,7 @@
       </c>
       <c r="H2" s="31" t="inlineStr">
         <is>
-          <t>CY2025</t>
+          <t>CY2026</t>
         </is>
       </c>
     </row>
@@ -2567,11 +2576,6 @@
       <c r="G3" s="31" t="inlineStr">
         <is>
           <t>for_profit</t>
-        </is>
-      </c>
-      <c r="H3" s="31" t="inlineStr">
-        <is>
-          <t>CY2026</t>
         </is>
       </c>
     </row>

--- a/nmtcapp/templates/pipeline_sample.xlsx
+++ b/nmtcapp/templates/pipeline_sample.xlsx
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -296,6 +296,8 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -661,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -694,12 +696,16 @@
     <col width="22" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="26" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CDE Profile — NMTC Application Builder v1.1  |  SAMPLE — FICTIONAL DATA. Riverbend Community Capital CDE, LLC does not exist and every value below is invented. Do NOT upload this file as your own application; use pipeline_template.xlsx.</t>
+          <t>CDE Profile — NMTC Application Builder v1.2  |  SAMPLE — FICTIONAL DATA. Riverbend Community Capital CDE, LLC does not exist and every value below is invented. Do NOT upload this file as your own application; use pipeline_template.xlsx.</t>
         </is>
       </c>
     </row>
@@ -734,6 +740,11 @@
           <t>Phase 2</t>
         </is>
       </c>
+      <c r="AE2" s="5" t="inlineStr">
+        <is>
+          <t>Contact &amp; Governance</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -886,6 +897,26 @@
           <t>Prior Reporting Issues (Y/N)</t>
         </is>
       </c>
+      <c r="AE3" s="7" t="inlineStr">
+        <is>
+          <t>Contact Name</t>
+        </is>
+      </c>
+      <c r="AF3" s="7" t="inlineStr">
+        <is>
+          <t>Contact Email</t>
+        </is>
+      </c>
+      <c r="AG3" s="7" t="inlineStr">
+        <is>
+          <t>Board Members</t>
+        </is>
+      </c>
+      <c r="AH3" s="7" t="inlineStr">
+        <is>
+          <t>Community Representatives</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -1010,6 +1041,22 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE4" s="8" t="inlineStr">
+        <is>
+          <t>Sarah Johnson</t>
+        </is>
+      </c>
+      <c r="AF4" s="8" t="inlineStr">
+        <is>
+          <t>sjohnson@riverbendcapital.org</t>
+        </is>
+      </c>
+      <c r="AG4" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH4" s="8" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -1019,15 +1066,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="Z2:AB2"/>
     <mergeCell ref="T2:Y2"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="L2:S2"/>
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="J2:K2"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="AE2:AH2"/>
   </mergeCells>
   <dataValidations count="9">
     <dataValidation sqref="O4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
@@ -1981,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1990,7 +2038,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>NMTC APPLICATION BUILDER — TEMPLATE v1.1 INSTRUCTIONS</t>
+          <t>NMTC APPLICATION BUILDER — TEMPLATE v1.2 INSTRUCTIONS</t>
         </is>
       </c>
     </row>
@@ -2431,6 +2479,55 @@
       <c r="A69" s="27" t="inlineStr">
         <is>
           <t>sub-criteria. Treat all scores as directional, not authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="33" t="inlineStr">
+        <is>
+          <t>NEW IN v1.2 — CONTACT &amp; GOVERNANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="34" t="inlineStr">
+        <is>
+          <t>'contact' and 'governance' are two of the eight fields a CDE profile requires, and</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="34" t="inlineStr">
+        <is>
+          <t>through v1.1 this sheet collected NEITHER — so a profile built from this workbook could</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="34" t="inlineStr">
+        <is>
+          <t>never be complete. Four columns now supply them:</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Contact Name, Contact Email            → contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Board Members, Community Representatives → governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="34" t="inlineStr">
+        <is>
+          <t>A v1.1 workbook still loads. It simply supplies neither field, exactly as before.</t>
         </is>
       </c>
     </row>
